--- a/attendance_forms/050_work_day_sign_in_form--attendance_forms.xlsx
+++ b/attendance_forms/050_work_day_sign_in_form--attendance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Name (2)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Name (3)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -825,9 +825,9 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -889,63 +889,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
